--- a/solutions/aws/ai/intelligent-document-processing/delivery/project-plan.xlsx
+++ b/solutions/aws/ai/intelligent-document-processing/delivery/project-plan.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>December 02, 2025</t>
+          <t>April 07, 2026</t>
         </is>
       </c>
     </row>
